--- a/text/foundationScores/shapessocial_3_seconds_MFT_MAC.xlsx
+++ b/text/foundationScores/shapessocial_3_seconds_MFT_MAC.xlsx
@@ -425,166 +425,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG58"/>
+  <dimension ref="A1:AI58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>chunkEnd</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>chunkStart</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>V_neu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>V_neg</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>V_pos</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>V_com</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sentence</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>full_text</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_virtue</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_virtue</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_virtue</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_virtue</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_care_vice</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_fairness_vice</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_loyalty_vice</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_authority_vice</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_sanctity_vice</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>MFT_a_moral_nonmoral</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_virtue</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_virtue</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_virtue</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_virtue</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_virtue</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_virtue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_virtue</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_fairness_vice</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_group_vice</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_deference_vice</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_heroism_vice</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_reciprocity_vice</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_family_vice</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_property_vice</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>MAC_a_moral_nonmoral</t>
         </is>
@@ -594,34 +604,38 @@
       <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>3.175</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.031</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>82</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
         <v>18</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>2.58</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Let's all go to the lobby.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -632,66 +646,72 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0.1694915254237288</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.1236559139784946</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.1185567010309278</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.0891089108910891</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.1036585365853658</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.4142857142857143</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.2467532467532468</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>0.1458333333333333</v>
       </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.2533333333333334</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AC2" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0.1463414634146341</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
       <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AI2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -699,104 +719,114 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>10.544</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.656</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>74.09999999999999</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
         <v>25.9</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>44.04</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t xml:space="preserve">  Let's all go to the lobby.  Let's all go to the lobby to get ourselves a treat.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.1016949152542373</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>0.0909090909090909</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.02898550724637681</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.04700854700854701</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.1129943502824859</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.08243727598566308</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.07903780068728523</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>0.0594059405940594</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.06910569105691056</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>1.5</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.0857142857142857</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>0.1159420289855072</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>0.3274725274725275</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>0.07971014492753624</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>0.2542457542457542</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>0.1849415204678363</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>0.02857142857142857</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>0.1688888888888889</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>0.1515151515151515</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
         <v>0.09756097560975609</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
       <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
         <v>0.04830917874396135</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -804,104 +834,114 @@
       <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16.992</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12.166</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
         <v>31.6</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>57.19</v>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t xml:space="preserve">  Delicious things to eat.  The popcorn can't be beat.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.07751937984496123</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.03846153846153847</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.07109799838019205</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.02729885057471264</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>0.1122073447654843</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.05061250805931657</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.01801801801801802</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>0.06346826586706646</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>0.13955463728191</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>1.5</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.06832298136645963</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.06725146198830409</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>0.1</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>0.1606263982102908</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>0.06521739130434782</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>0.1497524752475247</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>0.08</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>0.07777777777777778</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>0.05921052631578947</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
         <v>0.125</v>
       </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -909,34 +949,38 @@
       <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>22.399</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>17.012</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>83.3</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
         <v>16.7</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>29.6</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t xml:space="preserve">  The sparkling drinks are just dandy.  The chocolate bars and the candy.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -971,14 +1015,14 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
         <v>0.2592592592592592</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
@@ -986,27 +1030,33 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>0.2380952380952381</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>0.1904761904761905</v>
       </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
       <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
         <v>0.2727272727272727</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1014,34 +1064,38 @@
       <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26.224</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>22.419</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>89.09999999999999</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>10.9</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>2.58</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve"> So let's all go to the lobby to get ourselves</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
@@ -1052,66 +1106,72 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0.1694915254237288</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.1236559139784946</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.1185567010309278</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>0.0891089108910891</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>0.1036585365853658</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
         <v>0.4142857142857143</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
         <v>0.2467532467532468</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>0.1458333333333333</v>
       </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
         <v>0.2533333333333334</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
         <v>0.1463414634146341</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
       <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
         <v>0.07246376811594203</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1119,104 +1179,114 @@
       <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>49.519</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>30.811</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>71.09999999999999</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>7.5</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>21.3</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>51.06</v>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve"> To get ourselves a treat A young boy carrying a ball goes to an empty playground to play by himself.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.06033255247806715</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>0.07358818855665851</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.08042533473939859</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.03444580526638089</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.04073724680160324</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.08442716084234658</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.04244827095394618</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.03200693497618206</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>0.06742302249548626</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.05467836257309942</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>3</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>0.08698412698412698</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>0.1348350586611456</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>0.06276923076923077</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>0.07639751552795031</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>0.1011188811188811</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>0.1398110661268556</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>0.03819548872180451</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>0.0822426267804419</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>0.07333842627960276</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>0.1283580573054257</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>0.08811194202451622</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>0.06986324786324785</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>0.0583224115334207</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>0.06897635300175603</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -1224,104 +1294,114 @@
       <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>54.509</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>49.8</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy kicks the ball and then dashes after it.  He lines up his shot and kicks the ball again.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>0.0253968253968254</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.07512370670265407</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>0.2000183369209918</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.08617219247275076</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.04139433551198258</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>0.126791602542329</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.1062700865625785</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>0.6</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>0.07291666666666667</v>
       </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
       <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
         <v>0.05681818181818182</v>
       </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>0.05</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>0.05</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>0.1513157894736842</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>0.1902761104441777</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>0.3190730837789661</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>0.1</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>0.2208850931677019</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>0.04411764705882353</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>0.0234375</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1329,104 +1409,114 @@
       <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>61.302</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>54.769</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>100</v>
       </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boy catches up to the ball and bounces it off the playground's fences several times, passing it to himself.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.08260233918128655</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.1132113844895097</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>0.03544908155612595</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>0.01520912547528517</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>0.09212723200453261</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.07131248743790737</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>0.6</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>0.06269592476489028</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>0.103448275862069</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
         <v>0.0684633411449615</v>
       </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
         <v>0.02</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>0.1726315789473684</v>
       </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
         <v>0.04338842975206612</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>0.08142468944099379</v>
       </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
         <v>0.07602339181286549</v>
       </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -1434,104 +1524,114 @@
       <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>68.763</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>62.705</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>100</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve"> As he circles the ball, lining up his next shot, His father shows up and calls for him.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.01612903225806452</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.04723355430902601</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.07152349200868902</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.1177634247756199</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>0.07691577748724221</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>0.03104575163398693</v>
       </c>
-      <c r="P10" t="n">
+      <c r="R10" t="n">
         <v>0.1002369313165853</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>0.0910304980338619</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
         <v>0.04583333333333333</v>
       </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
         <v>0.021875</v>
       </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
         <v>0.03985507246376811</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Z10" t="n">
         <v>0.152141548327989</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AA10" t="n">
         <v>0.01851851851851852</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AB10" t="n">
         <v>0.1456066012488849</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AC10" t="n">
         <v>0.1600840336134454</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AD10" t="n">
         <v>0.119139304428668</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AE10" t="n">
         <v>0.1476324038937469</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AF10" t="n">
         <v>0.1154717484008529</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AG10" t="n">
         <v>0.04837461300309598</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AH10" t="n">
         <v>0.04411164446185998</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AI10" t="n">
         <v>1.333333333333333</v>
       </c>
     </row>
@@ -1539,104 +1639,114 @@
       <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>73.429</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>68.783</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>100</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boy takes one final kick at the ball before leaving the playground to meet his waiting father.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.0623053149183656</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.05100817488412831</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.05495727273538482</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.009966777408637875</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.04567226890756303</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.03558234327110025</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>0.03223016293477203</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>0.06380816932210399</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="S11" t="n">
         <v>0.0687941949279646</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>2.333333333333333</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>0.06745696400625978</v>
       </c>
-      <c r="T11" t="n">
+      <c r="V11" t="n">
         <v>0.036</v>
       </c>
-      <c r="U11" t="n">
+      <c r="W11" t="n">
         <v>0.0645734126984127</v>
       </c>
-      <c r="V11" t="n">
+      <c r="X11" t="n">
         <v>0.09710110677852614</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Y11" t="n">
         <v>0.05293668954996186</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Z11" t="n">
         <v>0.1823723723723724</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AA11" t="n">
         <v>0.07023584905660378</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AB11" t="n">
         <v>0.05612781954887218</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AC11" t="n">
         <v>0.1421541077671379</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AD11" t="n">
         <v>0.05065751858204688</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AE11" t="n">
         <v>0.05390749601275917</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AF11" t="n">
         <v>0.08092220279720279</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AG11" t="n">
         <v>0.06382978723404256</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AH11" t="n">
         <v>0.03339780786589297</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AI11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1644,104 +1754,114 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>80.479</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>73.69</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>95.39999999999999</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>4.6</v>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
         <v>-5.16</v>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy and his father exchange a few words and leave.  The boy and his father live in a modest two-story home with a pointed roof.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.04176430092083098</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.04495032358034819</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.04683574880097421</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
         <v>0.02176182637324554</v>
       </c>
-      <c r="L12" t="n">
+      <c r="N12" t="n">
         <v>0.0210290466465121</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.06940017868334321</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>0.06087497093708471</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>0.04168962230918539</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.06193495918384204</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.06460939908826237</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>12</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.08833574618199029</v>
       </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
         <v>0.05624349771119434</v>
       </c>
-      <c r="V12" t="n">
+      <c r="X12" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Y12" t="n">
         <v>0.100070531886974</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Z12" t="n">
         <v>0.2089660569138181</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AA12" t="n">
         <v>0.03462447478991597</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AB12" t="n">
         <v>0.07257463278449287</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AC12" t="n">
         <v>0.1707252474587785</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AD12" t="n">
         <v>0.05474255491670352</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AE12" t="n">
         <v>0.1366984601603887</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AF12" t="n">
         <v>0.05877077467986559</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AG12" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AH12" t="n">
         <v>0.07903441745036574</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AI12" t="n">
         <v>1.6</v>
       </c>
     </row>
@@ -1749,104 +1869,114 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>88.189</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>81.921</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>100</v>
       </c>
-      <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve"> After arriving home, they have a short chat, and the boy turns and climbs the stairs to his second-floor bedroom.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.006060606060606061</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>0.01271676300578035</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.04189473684210526</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0.02853078642552327</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>0.1050783293055106</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>0.07828014732316753</v>
       </c>
-      <c r="O13" t="n">
+      <c r="Q13" t="n">
         <v>0.02199161153629956</v>
       </c>
-      <c r="P13" t="n">
+      <c r="R13" t="n">
         <v>0.0934150544033866</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.04331090542709791</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.1093502781605675</v>
       </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
         <v>0.1138401559454191</v>
       </c>
-      <c r="V13" t="n">
+      <c r="X13" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Y13" t="n">
         <v>0.03755868544600939</v>
       </c>
-      <c r="X13" t="n">
+      <c r="Z13" t="n">
         <v>0.113981375175405</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AA13" t="n">
         <v>0.1631652661064426</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AB13" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AC13" t="n">
         <v>0.1605026022197422</v>
       </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
         <v>0.08007178432440061</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AF13" t="n">
         <v>0.06525573192239859</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AG13" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AH13" t="n">
         <v>0.04081632653061224</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AI13" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -1854,104 +1984,114 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>98.27</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>93.822</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>84.3</v>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
         <v>15.7</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>42.15</v>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve"> His father follows, gives his son a goodnight kiss and tucks him in for the night.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.01612903225806452</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.09858490566037736</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.03804125816993464</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.04244500698324022</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>0.02713178294573643</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>0.01608187134502924</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.05360843489240229</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.06385975887659193</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.07936507936507936</v>
       </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>0.02916666666666666</v>
       </c>
-      <c r="V14" t="n">
+      <c r="X14" t="n">
         <v>0.04761904761904762</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Y14" t="n">
         <v>0.1693259940542549</v>
       </c>
-      <c r="X14" t="n">
+      <c r="Z14" t="n">
         <v>0.4778126964173476</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AA14" t="n">
         <v>0.08852258852258853</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AB14" t="n">
         <v>0.06872058194266152</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AC14" t="n">
         <v>0.1787295240099618</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AD14" t="n">
         <v>0.1018075491759702</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AE14" t="n">
         <v>0.1106060606060606</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
-      </c>
       <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AI14" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -1959,104 +2099,114 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>108.748</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>99.672</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>100</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
         <is>
           <t xml:space="preserve"> While the boy falls asleep, his father walks back downstairs to his bedroom on the first floor, climbs into bed and quickly falls asleep.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.01290322580645161</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>0.01886792452830189</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.06246596292289903</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.1284492091853617</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>0.03482249386551406</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.07674677812608847</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.06610344163107325</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>0.625</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.04095593461265103</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>0.04225352112676056</v>
       </c>
-      <c r="U15" t="n">
+      <c r="W15" t="n">
         <v>0.06677892648287384</v>
       </c>
-      <c r="V15" t="n">
+      <c r="X15" t="n">
         <v>0.09895833333333333</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Y15" t="n">
         <v>0.09288537549407114</v>
       </c>
-      <c r="X15" t="n">
+      <c r="Z15" t="n">
         <v>0.2278586278586279</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AA15" t="n">
         <v>0.0625</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AB15" t="n">
         <v>0.02105263157894737</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AC15" t="n">
         <v>0.1029411764705882</v>
       </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
         <v>0.06926406926406926</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AF15" t="n">
         <v>0.0119047619047619</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AG15" t="n">
         <v>0.01041666666666667</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AH15" t="n">
         <v>0.08390151515151516</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AI15" t="n">
         <v>0.4444444444444444</v>
       </c>
     </row>
@@ -2064,88 +2214,92 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>119.526</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>110.731</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>81.5</v>
       </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>18.5</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>51.06</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Upstairs, the boy begins to dream.  The ceiling opens up and he floats into the sky along with a huge bird.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.04289194855232591</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.06542744486329563</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.1017232837541966</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.05694150810429879</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>0.06020775916896332</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>0.06</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>0.01492537313432836</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.04242424242424242</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.325</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="U16" t="n">
+      <c r="W16" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="V16" t="n">
+      <c r="X16" t="n">
         <v>0.03773584905660377</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Y16" t="n">
         <v>0.1016949152542373</v>
       </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
         <v>0.07547169811320754</v>
       </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
       <c r="AB16" t="n">
         <v>0</v>
       </c>
@@ -2162,6 +2316,12 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -2169,104 +2329,114 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>132.925</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>122.543</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>100</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t xml:space="preserve">  High above mountains, the boy can fly.  The giant bird splits into two smaller birds which soar across the sky with the boy.</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.006896551724137929</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.02758620689655172</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.04912280701754386</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.02420749279538905</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>0.02427745664739884</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.1042214076246334</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>0.07252324237398865</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>0.06756651258346173</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.1129461279461279</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.08284600389863547</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
         <v>0.2207792207792208</v>
       </c>
-      <c r="U17" t="n">
+      <c r="W17" t="n">
         <v>0.1503267973856209</v>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
       <c r="X17" t="n">
         <v>0</v>
       </c>
       <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AB17" t="n">
         <v>0.3306451612903226</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
       <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
         <v>0.1304347826086956</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AF17" t="n">
         <v>0.2</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AG17" t="n">
         <v>0.1121495327102804</v>
       </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
         <v>0.09090909090909091</v>
       </c>
     </row>
@@ -2274,67 +2444,71 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>142.947</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>135.554</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>93.89999999999999</v>
       </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
         <v>6.1</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>12.8</v>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t xml:space="preserve">  The two birds become four birds.  The boy plays with the birds, but then the flock gangs up on him and starts chasing him.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
         <v>0.06140350877192983</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>0.2358333333333333</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>0.1223880597014925</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>0.1041666666666667</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.06363636363636363</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.1326315789473684</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>0.2857142857142857</v>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
@@ -2372,6 +2546,12 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2379,67 +2559,71 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>148.958</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>143.188</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>55.50000000000001</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>32.9</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>11.6</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>-56.10000000000001</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve">  He tries to fly away but cannot escape.  Thankfully, the dream ends and the birds disappear.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.04643108870093255</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.03659394792399718</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.02874680904178646</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.009090909090909089</v>
       </c>
-      <c r="L19" t="n">
+      <c r="N19" t="n">
         <v>0.04159519725557461</v>
       </c>
-      <c r="M19" t="n">
+      <c r="O19" t="n">
         <v>0.05350187452307489</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>0.08304542781534843</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>0.07362557085489736</v>
       </c>
-      <c r="P19" t="n">
+      <c r="R19" t="n">
         <v>0.1241051194704163</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="S19" t="n">
         <v>0.07218606417324365</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
@@ -2447,36 +2631,42 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
         <v>0.1380952380952381</v>
       </c>
-      <c r="X19" t="n">
+      <c r="Z19" t="n">
         <v>0.211142993782879</v>
       </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
         <v>0.2365220249835635</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AC19" t="n">
         <v>0.2154761904761905</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AD19" t="n">
         <v>0.1373299319727891</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="n">
         <v>0.1020408163265306</v>
       </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
       <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
         <v>0.09292035398230089</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AI19" t="n">
         <v>0.2857142857142857</v>
       </c>
     </row>
@@ -2484,104 +2674,114 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>159.216</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>149.899</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
         <v>11.6</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>52.66999999999999</v>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy sleeps peacefully for the rest of the night.  In the morning, the boy's father climbs the stairs to his son's bedroom and wakes him up.</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.06378299120234605</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.07059754270582819</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.07643495994889184</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.06168558217738546</v>
       </c>
-      <c r="L20" t="n">
+      <c r="N20" t="n">
         <v>0.02964426877470356</v>
       </c>
-      <c r="M20" t="n">
+      <c r="O20" t="n">
         <v>0.08048417132216014</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>0.03301322843148598</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>0.01072124756335283</v>
       </c>
-      <c r="P20" t="n">
+      <c r="R20" t="n">
         <v>0.06514236568584393</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="S20" t="n">
         <v>0.06918631561145379</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="S20" t="n">
+      <c r="U20" t="n">
         <v>0.06818181818181819</v>
       </c>
-      <c r="T20" t="n">
+      <c r="V20" t="n">
         <v>0.05128205128205129</v>
       </c>
-      <c r="U20" t="n">
+      <c r="W20" t="n">
         <v>0.0837121212121212</v>
       </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
         <v>0.1052234299516908</v>
       </c>
-      <c r="X20" t="n">
+      <c r="Z20" t="n">
         <v>0.4786673972720485</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AA20" t="n">
         <v>0.08376068376068375</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AB20" t="n">
         <v>0.06872058194266152</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AC20" t="n">
         <v>0.1399698340874811</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AD20" t="n">
         <v>0.06140350877192982</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AE20" t="n">
         <v>0.1432857991681521</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AF20" t="n">
         <v>0.05691056910569106</v>
       </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AI20" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -2589,104 +2789,114 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>169.489</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>165.743</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
         <v>100</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0</v>
-      </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boy follows his father down the stairs to the first floor of their home.</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.01290322580645161</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.0588679245283019</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.04874441004471965</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0.03092313092313093</v>
       </c>
-      <c r="M21" t="n">
+      <c r="O21" t="n">
         <v>0.08079261501979632</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>0.04191651095953115</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>0.01686340640809444</v>
       </c>
-      <c r="P21" t="n">
+      <c r="R21" t="n">
         <v>0.06697647506158144</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="S21" t="n">
         <v>0.04594840287138333</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>5</v>
       </c>
-      <c r="S21" t="n">
+      <c r="U21" t="n">
         <v>0.1093502781605675</v>
       </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
         <v>0.1121426250812216</v>
       </c>
-      <c r="V21" t="n">
+      <c r="X21" t="n">
         <v>0.05555555555555555</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Y21" t="n">
         <v>0.09069878206436688</v>
       </c>
-      <c r="X21" t="n">
+      <c r="Z21" t="n">
         <v>0.2716390328330627</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AA21" t="n">
         <v>0.1631652661064426</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AB21" t="n">
         <v>0.02807017543859649</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AC21" t="n">
         <v>0.1864995178399228</v>
       </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
         <v>0.1024264788102427</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AF21" t="n">
         <v>0.01587301587301587</v>
       </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AI21" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2694,104 +2904,114 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>173.034</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>169.709</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
         <v>100</v>
       </c>
-      <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0</v>
-      </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t xml:space="preserve"> They have a brief conversation before the boy heads out for the day.</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.01488095238095238</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.0482841719683825</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0.03680172620474706</v>
       </c>
-      <c r="M22" t="n">
+      <c r="O22" t="n">
         <v>0.08123990622557957</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>0.01220891483044857</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.01578947368421053</v>
       </c>
-      <c r="P22" t="n">
+      <c r="R22" t="n">
         <v>0.05462169714426206</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.02670580507430823</v>
       </c>
-      <c r="R22" t="n">
+      <c r="T22" t="n">
         <v>4</v>
       </c>
-      <c r="S22" t="n">
+      <c r="U22" t="n">
         <v>0.06944444444444445</v>
       </c>
-      <c r="T22" t="n">
+      <c r="V22" t="n">
         <v>0.05</v>
       </c>
-      <c r="U22" t="n">
+      <c r="W22" t="n">
         <v>0.06074586697424067</v>
       </c>
-      <c r="V22" t="n">
+      <c r="X22" t="n">
         <v>0.04</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Y22" t="n">
         <v>0.01245551601423488</v>
       </c>
-      <c r="X22" t="n">
+      <c r="Z22" t="n">
         <v>0.05405405405405406</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
         <v>0.03275355771402755</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AB22" t="n">
         <v>0.009652509652509652</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AC22" t="n">
         <v>0.015625</v>
       </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
         <v>0.005226480836236934</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AF22" t="n">
         <v>0.07608695652173914</v>
       </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
       <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2799,104 +3019,114 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>185.032</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>173.655</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>100</v>
       </c>
-      <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0</v>
-      </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve">  The day passes.  The father waits for his son to return home.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.01290322580645161</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.01886792452830189</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.04776241857689822</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0.01274131274131274</v>
       </c>
-      <c r="M23" t="n">
+      <c r="O23" t="n">
         <v>0.07175565525623713</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>0.06795633977935642</v>
       </c>
-      <c r="O23" t="n">
+      <c r="Q23" t="n">
         <v>0.02972890348411783</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>0.06137424969659223</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.06111983081877997</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>2.5</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>0.04180064308681672</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>0.01785714285714286</v>
       </c>
-      <c r="U23" t="n">
+      <c r="W23" t="n">
         <v>0.08709625339195069</v>
       </c>
-      <c r="V23" t="n">
+      <c r="X23" t="n">
         <v>0.02765957446808511</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Y23" t="n">
         <v>0.117182087889212</v>
       </c>
-      <c r="X23" t="n">
+      <c r="Z23" t="n">
         <v>0.3581533660325746</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AA23" t="n">
         <v>0.08398649116990151</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AB23" t="n">
         <v>0.09031074433094861</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AC23" t="n">
         <v>0.1315433758623248</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AD23" t="n">
         <v>0.03684210526315789</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AE23" t="n">
         <v>0.09354647962064036</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
       <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
         <v>0.01212121212121212</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AI23" t="n">
         <v>2.5</v>
       </c>
     </row>
@@ -2904,104 +3134,114 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>192.683</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>185.833</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
         <v>100</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve">  When he does, the two talk briefly.  The boy climbs into bed as does his father downstairs.</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.01290322580645161</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.05192176389282086</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.06272373821009433</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
         <v>0.02085308056872038</v>
       </c>
-      <c r="L24" t="n">
+      <c r="N24" t="n">
         <v>0.01271676300578035</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.1336728763489479</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>0.008955223880597014</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>0.01714285714285715</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.03858585858585858</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.05588629107014111</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>2.5</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.03070175438596491</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>0.03864734299516908</v>
       </c>
-      <c r="U24" t="n">
+      <c r="W24" t="n">
         <v>0.1057432432432432</v>
       </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
         <v>0.1000884534258692</v>
       </c>
-      <c r="X24" t="n">
+      <c r="Z24" t="n">
         <v>0.3248892960757368</v>
       </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
         <v>0.02807017543859649</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AC24" t="n">
         <v>0.09803921568627451</v>
       </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
         <v>0.1492626614577834</v>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
-      </c>
       <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
         <v>0.0372960372960373</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AI24" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -3009,104 +3249,114 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>202.521</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>192.904</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>80.60000000000001</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>8.6</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>10.8</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>10.27</v>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Both fall right asleep.  Shortly after falling asleep, the boy starts to have the bird dream again.</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.0421192338044336</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>0.05020275211061622</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.07050141137204352</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0393354868481772</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>0.02264150943396227</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.09135714285714286</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>0.02269568189586419</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>0.04222222222222222</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.04610454545454545</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.1012771031068686</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>1</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.1796157059314954</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.1076190476190476</v>
       </c>
-      <c r="U25" t="n">
+      <c r="W25" t="n">
         <v>0.1645718116306352</v>
       </c>
-      <c r="V25" t="n">
+      <c r="X25" t="n">
         <v>0.06511627906976744</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Y25" t="n">
         <v>0.06008583690987124</v>
       </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.1094017094017094</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AA25" t="n">
         <v>0.04385964912280702</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AF25" t="n">
         <v>0.02424242424242424</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AG25" t="n">
         <v>0.04972375690607735</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AH25" t="n">
         <v>0.03703703703703703</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AI25" t="n">
         <v>0.4285714285714285</v>
       </c>
     </row>
@@ -3114,67 +3364,71 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>205.993</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>202.882</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>100</v>
       </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t xml:space="preserve"> The four birds from the previous night are back.</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
       <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>0.0594059405940594</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.06299212598425198</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
         <v>0.032</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.064</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
       <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.5</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
       <c r="U26" t="n">
         <v>0</v>
       </c>
@@ -3182,29 +3436,29 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
         <v>0.108695652173913</v>
       </c>
-      <c r="X26" t="n">
+      <c r="Z26" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
         <v>0.03636363636363636</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AB26" t="n">
         <v>0.07017543859649122</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AC26" t="n">
         <v>0.1571428571428571</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AD26" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
@@ -3212,6 +3466,12 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3219,104 +3479,114 @@
       <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>210.448</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>206.013</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>74.8</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>16.3</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>9</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>0.67</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t xml:space="preserve"> They surround him, preventing him from escaping no matter which direction he turns.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
         <v>0.04301075268817204</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.07106446776611694</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.1555004135649297</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.02284946236559139</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.1595208300227766</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.07981715893108297</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.03947368421052632</v>
       </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>0.06581196581196581</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>0.1352265043948614</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>0.1153846153846154</v>
       </c>
-      <c r="U27" t="n">
+      <c r="W27" t="n">
         <v>0.06198347107438017</v>
       </c>
-      <c r="V27" t="n">
+      <c r="X27" t="n">
         <v>0.06</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Y27" t="n">
         <v>0.07203389830508475</v>
       </c>
-      <c r="X27" t="n">
+      <c r="Z27" t="n">
         <v>0.0410958904109589</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AA27" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
         <v>0.04477611940298507</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AD27" t="n">
         <v>0.09259259259259259</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AE27" t="n">
         <v>0.04065040650406504</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AG27" t="n">
         <v>0.125</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.05714285714285714</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -3324,104 +3594,114 @@
       <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>218.392</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>213.787</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>100</v>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t xml:space="preserve"> The birds transform into a giant monster with two long arms and two wobbly legs.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.04612529422415354</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.02470930232558139</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
         <v>0.02</v>
       </c>
-      <c r="L28" t="n">
+      <c r="N28" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.1946480432903734</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.08244087460954931</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.073125</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.09238006038917468</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.06526104417670682</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>1</v>
       </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
       <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
         <v>0.09731543624161074</v>
       </c>
-      <c r="X28" t="n">
+      <c r="Z28" t="n">
         <v>0.1229763387297634</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AA28" t="n">
         <v>0.05298013245033113</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AB28" t="n">
         <v>0.2165372316126085</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AC28" t="n">
         <v>0.07489878542510121</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AD28" t="n">
         <v>0.09836065573770492</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AE28" t="n">
         <v>0.1383458646616541</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AF28" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AI28" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -3429,67 +3709,71 @@
       <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>222.437</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>218.612</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>84</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>16</v>
       </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>-22.63</v>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t xml:space="preserve">  The monster swats at the boy.  He misses and tries again.</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.09375</v>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
         <v>0.06140350877192983</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.06818181818181818</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.09</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.1682213930348259</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0925925925925926</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.1826839826839827</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
@@ -3527,6 +3811,12 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3534,67 +3824,71 @@
       <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>226.441</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>222.477</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
         <v>75.59999999999999</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>24.4</v>
       </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>-44.04</v>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t xml:space="preserve"> Frightened, the boy flies over the monster, evading its grasp.</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>0.1228070175438597</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>0.18</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>0.04477611940298507</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.1272727272727273</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.1052631578947368</v>
       </c>
-      <c r="R30" t="n">
+      <c r="T30" t="n">
         <v>0.2</v>
       </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
       <c r="U30" t="n">
         <v>0</v>
       </c>
@@ -3632,6 +3926,12 @@
         <v>0</v>
       </c>
       <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3639,104 +3939,114 @@
       <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>230.866</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>226.762</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>100</v>
       </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t xml:space="preserve">  The monster scrunches into a little ball.  It pounces, lunging at the boy.</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>0.1067368421052632</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.03252032520325204</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.1346685878962536</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>0.07581271723573911</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.06363636363636363</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.09508440913604765</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>0.4</v>
       </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
         <v>0.07017543859649122</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Y31" t="n">
         <v>0.1409395973154362</v>
       </c>
-      <c r="X31" t="n">
+      <c r="Z31" t="n">
         <v>0.1491228070175439</v>
       </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
         <v>0.1849315068493151</v>
       </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
         <v>0.125</v>
       </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
         <v>0.05797101449275362</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AI31" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -3744,104 +4054,114 @@
       <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>234.631</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>231.107</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
         <v>71.3</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>28.7</v>
       </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
         <v>-56.10000000000001</v>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t xml:space="preserve"> After the boy dodges this attack, the nightmare finally ends.</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.02319587628865979</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.02850877192982456</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.05039872408293461</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0.01126126126126126</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.1332716049382716</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>0.04820701686373328</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.03648648648648649</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>0.09830051261320787</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.06996342368660505</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>2</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>0.09166666666666667</v>
       </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
         <v>0.06802721088435375</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Y32" t="n">
         <v>0.1106821106821107</v>
       </c>
-      <c r="X32" t="n">
+      <c r="Z32" t="n">
         <v>0.07843137254901961</v>
       </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
         <v>0.1697530864197531</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AC32" t="n">
         <v>0.2190390970466532</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>0.1832251082251082</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AE32" t="n">
         <v>0.07645259938837921</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
         <v>0.05734767025089606</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AG32" t="n">
         <v>0.07096171802054155</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AH32" t="n">
         <v>0.06998461876510657</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AI32" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3849,104 +4169,114 @@
       <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>247.476</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>235.632</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>89.5</v>
       </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
         <v>10.5</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>52.66999999999999</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy sleeps peacefully for the rest of the night.  In the morning, the boy's dad wakes up, walks to the stairs and shouts for his son to come down.</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.06637605101292253</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>0.05487427226557661</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.0771417969908247</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.07790695622318698</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>0.04138135797658149</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.08048417132216014</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.04684722052634763</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.01072124756335283</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>0.054199604743083</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>0.05206302794022092</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>0.75</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>0.06818181818181819</v>
       </c>
-      <c r="T33" t="n">
+      <c r="V33" t="n">
         <v>0.05128205128205129</v>
       </c>
-      <c r="U33" t="n">
+      <c r="W33" t="n">
         <v>0.08944946850706013</v>
       </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
         <v>0.08572247706422019</v>
       </c>
-      <c r="X33" t="n">
+      <c r="Z33" t="n">
         <v>0.3644022445453572</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AA33" t="n">
         <v>0.09603062241099052</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AB33" t="n">
         <v>0.09620596205962058</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AC33" t="n">
         <v>0.1028490028490028</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AD33" t="n">
         <v>0.06140350877192982</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AE33" t="n">
         <v>0.1329080490643746</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AF33" t="n">
         <v>0.05691056910569106</v>
       </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
       <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>0.2727272727272727</v>
       </c>
     </row>
@@ -3954,104 +4284,114 @@
       <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>257.912</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>247.637</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
         <v>89.60000000000001</v>
       </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
         <v>10.4</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>44.04</v>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy jumps up and goes down the stairs.  After a brief good morning, the boy again heads out for the day and the day passes.</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.01584266593826824</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.02106570774762995</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.06935749908910269</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.01204250295159386</v>
       </c>
-      <c r="L34" t="n">
+      <c r="N34" t="n">
         <v>0.03728420684069995</v>
       </c>
-      <c r="M34" t="n">
+      <c r="O34" t="n">
         <v>0.08056796878688958</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.01395304552051265</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.05516312320389534</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>0.03052092008492369</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>1.4</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>0.04333333333333333</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>0.07204545454545455</v>
       </c>
-      <c r="U34" t="n">
+      <c r="W34" t="n">
         <v>0.03541009163846534</v>
       </c>
-      <c r="V34" t="n">
+      <c r="X34" t="n">
         <v>0.0414572864321608</v>
       </c>
-      <c r="W34" t="n">
+      <c r="Y34" t="n">
         <v>0.05186438300930877</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Z34" t="n">
         <v>0.06153421633554083</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="AA34" t="n">
         <v>0.02869804221294608</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="AB34" t="n">
         <v>0.06067291781577495</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AC34" t="n">
         <v>0.015625</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>0.03070175438596491</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AE34" t="n">
         <v>0.02308362369337979</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AF34" t="n">
         <v>0.03205128205128205</v>
       </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
         <v>0.02027027027027027</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AI34" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -4059,104 +4399,114 @@
       <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>272.926</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>262.879</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
         <v>14.9</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>36.12</v>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t xml:space="preserve"> At the end of the day, the boy returns home, greets his father quickly, and then goes straight upstairs to his bedroom.</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.008064516129032258</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.03502298872503196</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.04974500392403161</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.007978723404255319</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.01869020134106341</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.07556068099173725</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.03870563891346461</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.03035956637457886</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>0.07091676193823744</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.04662359281658979</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>2</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>0.04229655580617811</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>0.04816901408450704</v>
       </c>
-      <c r="U35" t="n">
+      <c r="W35" t="n">
         <v>0.07019350768629891</v>
       </c>
-      <c r="V35" t="n">
+      <c r="X35" t="n">
         <v>0.03819444444444444</v>
       </c>
-      <c r="W35" t="n">
+      <c r="Y35" t="n">
         <v>0.08485476505713041</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Z35" t="n">
         <v>0.1571870377840527</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="AA35" t="n">
         <v>0.04206188913333574</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="AB35" t="n">
         <v>0.07247831759109954</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AC35" t="n">
         <v>0.1033812736470644</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AD35" t="n">
         <v>0.04674041425402586</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AE35" t="n">
         <v>0.08952002553420711</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AF35" t="n">
         <v>0.03794692799928401</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AG35" t="n">
         <v>0.01960267229254571</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AH35" t="n">
         <v>0.08428206288153932</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AI35" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4164,104 +4514,114 @@
       <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>278.873</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>275.609</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>100</v>
       </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boy climbs into bed, as does his father downstairs.</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.02150537634408602</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>0.03144654088050314</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.07198142414860682</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>0.1340740740740741</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.01492537313432836</v>
       </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
         <v>0.0643097643097643</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.06933429464071135</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>1.5</v>
       </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
       <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
         <v>0.04375</v>
       </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
         <v>0.07971014492753623</v>
       </c>
-      <c r="X36" t="n">
+      <c r="Z36" t="n">
         <v>0.4364864864864865</v>
       </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
         <v>0.04210526315789474</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AC36" t="n">
         <v>0.1470588235294118</v>
       </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
         <v>0.1385281385281385</v>
       </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
       <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.0303030303030303</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -4269,104 +4629,114 @@
       <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>284.76</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>279.453</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>88.2</v>
       </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
         <v>11.8</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>25</v>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t xml:space="preserve">  Both eventually fall asleep.  For the third night in a row, the boy begins to dream.</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.03132075471698113</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.02024809923969587</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.04816972007483498</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.03659716430358632</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.06509675240071418</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.08421428571428571</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.06269568189586419</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.02762762762762763</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>0.03985454545454545</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.04241185487991824</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>0.1547619047619048</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.06</v>
       </c>
-      <c r="U37" t="n">
+      <c r="W37" t="n">
         <v>0.1088235294117647</v>
       </c>
-      <c r="V37" t="n">
+      <c r="X37" t="n">
         <v>0.09375</v>
       </c>
-      <c r="W37" t="n">
+      <c r="Y37" t="n">
         <v>0.06944444444444445</v>
       </c>
-      <c r="X37" t="n">
+      <c r="Z37" t="n">
         <v>0.0641025641025641</v>
       </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
       <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
         <v>0.05357142857142857</v>
       </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
         <v>0.0625</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AF37" t="n">
         <v>0.03636363636363636</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AG37" t="n">
         <v>0.06818181818181818</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>0.1290849673202614</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -4374,104 +4744,114 @@
       <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>295.132</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>288.705</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
         <v>82.59999999999999</v>
       </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
         <v>17.4</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>42.15</v>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t xml:space="preserve"> The towering monster from the previous dream appears again, slowly following the boy and reaching for him with one arm.</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.009433962264150943</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.02269635126777983</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.0638262340074882</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
         <v>0.03656490539692639</v>
       </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
         <v>0.02269934215282296</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.08508802981979256</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.03752970596751691</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.01412429378531073</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.05039679421701893</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.03969448121249605</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>1.5</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.1423728813559322</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.2003918495297806</v>
       </c>
-      <c r="U38" t="n">
+      <c r="W38" t="n">
         <v>0.01923076923076923</v>
       </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
         <v>0.1083622117534292</v>
       </c>
-      <c r="X38" t="n">
+      <c r="Z38" t="n">
         <v>0.03947368421052631</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA38" t="n">
         <v>0.02832167832167832</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB38" t="n">
         <v>0.03867062021250309</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AC38" t="n">
         <v>0.03928571428571428</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AD38" t="n">
         <v>0.0418613707165109</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AE38" t="n">
         <v>0.1377389971139971</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.01102941176470588</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AH38" t="n">
         <v>0.04880952380952381</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -4479,104 +4859,114 @@
       <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>300.679</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>295.913</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
         <v>77.40000000000001</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>15.5</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>7.1</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>-31.82</v>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boy stays out of his reach and hovers uncertainly around the monster's feet.</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.04580152671755725</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>0.04482758620689655</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.06140350877192983</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.04365079365079365</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.008695652173913044</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.09</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.02238805970149254</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.03146853146853147</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.06363636363636363</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.4</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>0.2181818181818182</v>
       </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
         <v>0.163265306122449</v>
       </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
         <v>0.171875</v>
       </c>
-      <c r="X39" t="n">
+      <c r="Z39" t="n">
         <v>0.1463414634146341</v>
       </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
       <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
         <v>0.1777777777777778</v>
       </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
         <v>0.1818181818181818</v>
       </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
       <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
         <v>0.1020408163265306</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -4584,104 +4974,114 @@
       <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>308.554</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>302.566</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
         <v>79.5</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>13.6</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>6.800000000000001</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>-29.6</v>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t xml:space="preserve">  Suddenly he is joined by another boy.  The boys speak frantically as the monster reaches down.</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.01793493245106149</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>0.01578947368421053</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.04561403508771929</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.04596273291925466</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.01720430107526882</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.09170228091236494</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.05635359786433686</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.05143572181243414</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.06877515614156834</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>0.08586685915677095</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>1.666666666666667</v>
       </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
         <v>0.1122448979591837</v>
       </c>
-      <c r="U40" t="n">
+      <c r="W40" t="n">
         <v>0.2</v>
       </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
         <v>0.05405405405405406</v>
       </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="AB40" t="n">
         <v>0.1359649122807017</v>
       </c>
-      <c r="AA40" t="n">
+      <c r="AC40" t="n">
         <v>0.09183673469387756</v>
       </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
         <v>0.1950185479597244</v>
       </c>
-      <c r="AD40" t="n">
+      <c r="AF40" t="n">
         <v>0.06097560975609756</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.1658653846153846</v>
       </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -4689,67 +5089,71 @@
       <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>311.998</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>308.714</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
         <v>100</v>
       </c>
-      <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boys fly over the monster which is still clawing at them.</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>0.01724137931034482</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>0.06896551724137931</v>
       </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>0.04347826086956521</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
         <v>0.08823529411764706</v>
       </c>
-      <c r="N41" t="n">
+      <c r="P41" t="n">
         <v>0.04878048780487805</v>
       </c>
-      <c r="O41" t="n">
+      <c r="Q41" t="n">
         <v>0.09702797202797203</v>
       </c>
-      <c r="P41" t="n">
+      <c r="R41" t="n">
         <v>0.0925925925925926</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="S41" t="n">
         <v>0.1328976034858388</v>
       </c>
-      <c r="R41" t="n">
+      <c r="T41" t="n">
         <v>1</v>
       </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
@@ -4787,6 +5191,12 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4794,104 +5204,114 @@
       <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>317.645</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>312.719</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
         <v>88.09999999999999</v>
       </c>
-      <c r="C42" t="n">
+      <c r="E42" t="n">
         <v>11.9</v>
       </c>
-      <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
         <v>-31.82</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boys make a desperate plan and the new boy speeds away.  He quickly returns with the ball.</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>0.0100864553314121</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>0.03510832578701405</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>0.03399794490997765</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
         <v>0.02735209452079029</v>
       </c>
-      <c r="L42" t="n">
+      <c r="N42" t="n">
         <v>0.01766053345454722</v>
       </c>
-      <c r="M42" t="n">
+      <c r="O42" t="n">
         <v>0.08385669378484892</v>
       </c>
-      <c r="N42" t="n">
+      <c r="P42" t="n">
         <v>0.05980837250316347</v>
       </c>
-      <c r="O42" t="n">
+      <c r="Q42" t="n">
         <v>0.04899692690058437</v>
       </c>
-      <c r="P42" t="n">
+      <c r="R42" t="n">
         <v>0.06593864289446186</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="S42" t="n">
         <v>0.06216463341518119</v>
       </c>
-      <c r="R42" t="n">
+      <c r="T42" t="n">
         <v>4</v>
       </c>
-      <c r="S42" t="n">
+      <c r="U42" t="n">
         <v>0.01119402985074627</v>
       </c>
-      <c r="T42" t="n">
+      <c r="V42" t="n">
         <v>0.08291617172917021</v>
       </c>
-      <c r="U42" t="n">
+      <c r="W42" t="n">
         <v>0.03174603174603174</v>
       </c>
-      <c r="V42" t="n">
+      <c r="X42" t="n">
         <v>0.1084651350292362</v>
       </c>
-      <c r="W42" t="n">
+      <c r="Y42" t="n">
         <v>0.1029749320446995</v>
       </c>
-      <c r="X42" t="n">
+      <c r="Z42" t="n">
         <v>0.06249599897573779</v>
       </c>
-      <c r="Y42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" t="n">
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
         <v>0.1113665293780797</v>
       </c>
-      <c r="AA42" t="n">
+      <c r="AC42" t="n">
         <v>0.07205788804071248</v>
       </c>
-      <c r="AB42" t="n">
+      <c r="AD42" t="n">
         <v>0.09980199766139675</v>
       </c>
-      <c r="AC42" t="n">
+      <c r="AE42" t="n">
         <v>0.05102040816326531</v>
       </c>
-      <c r="AD42" t="n">
+      <c r="AF42" t="n">
         <v>0.0341726618705036</v>
       </c>
-      <c r="AE42" t="n">
+      <c r="AG42" t="n">
         <v>0.02048860911270983</v>
       </c>
-      <c r="AF42" t="n">
+      <c r="AH42" t="n">
         <v>0.1619086539527853</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AI42" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -4899,104 +5319,114 @@
       <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>325.676</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>318.767</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
         <v>100</v>
       </c>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boys pull the ball in a slingshot.  But the last minute they let it go, shooting the ball into the monster which breaks into a heap.</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>0.0217391304347826</v>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
         <v>0.1688586107828381</v>
       </c>
-      <c r="N43" t="n">
+      <c r="P43" t="n">
         <v>0.0714332546551272</v>
       </c>
-      <c r="O43" t="n">
+      <c r="Q43" t="n">
         <v>0.1220288592171834</v>
       </c>
-      <c r="P43" t="n">
+      <c r="R43" t="n">
         <v>0.05913620208174664</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="S43" t="n">
         <v>0.1218271100897771</v>
       </c>
-      <c r="R43" t="n">
+      <c r="T43" t="n">
         <v>0.5714285714285714</v>
       </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
       <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
         <v>0.2071428571428572</v>
       </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
         <v>0.1233766233766234</v>
       </c>
-      <c r="X43" t="n">
+      <c r="Z43" t="n">
         <v>0.07291666666666667</v>
       </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
         <v>0.1674829931972789</v>
       </c>
-      <c r="AA43" t="n">
+      <c r="AC43" t="n">
         <v>0.2214795008912656</v>
       </c>
-      <c r="AB43" t="n">
+      <c r="AD43" t="n">
         <v>0.05952380952380952</v>
       </c>
-      <c r="AC43" t="n">
+      <c r="AE43" t="n">
         <v>0.2270168855534709</v>
       </c>
-      <c r="AD43" t="n">
+      <c r="AF43" t="n">
         <v>0.125</v>
       </c>
-      <c r="AE43" t="n">
+      <c r="AG43" t="n">
         <v>0.06122448979591837</v>
       </c>
-      <c r="AF43" t="n">
+      <c r="AH43" t="n">
         <v>0.09575569358178054</v>
       </c>
-      <c r="AG43" t="n">
+      <c r="AI43" t="n">
         <v>0.2222222222222222</v>
       </c>
     </row>
@@ -5004,67 +5434,71 @@
       <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>334.415</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>325.896</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
         <v>86.2</v>
       </c>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
         <v>13.8</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
         <v>34</v>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t xml:space="preserve">  Excited, the boy swoops over the heap.  until he notices that the other boy is gone.</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>0.08187134502923978</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
       <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
         <v>0.1523624595469256</v>
       </c>
-      <c r="N44" t="n">
+      <c r="P44" t="n">
         <v>0.06352077993869037</v>
       </c>
-      <c r="O44" t="n">
+      <c r="Q44" t="n">
         <v>0.03846153846153847</v>
       </c>
-      <c r="P44" t="n">
+      <c r="R44" t="n">
         <v>0.09179292929292927</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="S44" t="n">
         <v>0.08620107962213225</v>
       </c>
-      <c r="R44" t="n">
+      <c r="T44" t="n">
         <v>0.75</v>
       </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
@@ -5072,36 +5506,42 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
         <v>0.2181818181818182</v>
       </c>
-      <c r="X44" t="n">
+      <c r="Z44" t="n">
         <v>0.08695652173913043</v>
       </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
         <v>0.2608695652173913</v>
       </c>
-      <c r="AA44" t="n">
+      <c r="AC44" t="n">
         <v>0.12</v>
       </c>
-      <c r="AB44" t="n">
+      <c r="AD44" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="AC44" t="n">
+      <c r="AE44" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
       <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
         <v>0.1142857142857143</v>
       </c>
-      <c r="AG44" t="n">
+      <c r="AI44" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -5109,104 +5549,114 @@
       <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>344.988</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>339.722</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
         <v>72.59999999999999</v>
       </c>
-      <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="n">
+      <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
         <v>27.4</v>
       </c>
-      <c r="E45" t="n">
+      <c r="G45" t="n">
         <v>75.06</v>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t xml:space="preserve">  He goes looking for his new friend but can't find him.  He checks under the rubble for his friend.</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>0.03116679657655293</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>0.06327514252868986</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>0.06087842016555173</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
         <v>0.03927528555961247</v>
       </c>
-      <c r="L45" t="n">
+      <c r="N45" t="n">
         <v>0.03814948161581837</v>
       </c>
-      <c r="M45" t="n">
+      <c r="O45" t="n">
         <v>0.05261038252937528</v>
       </c>
-      <c r="N45" t="n">
+      <c r="P45" t="n">
         <v>0.03238095238095238</v>
       </c>
-      <c r="O45" t="n">
+      <c r="Q45" t="n">
         <v>0.02921985815602837</v>
       </c>
-      <c r="P45" t="n">
+      <c r="R45" t="n">
         <v>0.07351384142301574</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="S45" t="n">
         <v>0.02227272727272728</v>
       </c>
-      <c r="R45" t="n">
+      <c r="T45" t="n">
         <v>7</v>
       </c>
-      <c r="S45" t="n">
+      <c r="U45" t="n">
         <v>0.181025641025641</v>
       </c>
-      <c r="T45" t="n">
+      <c r="V45" t="n">
         <v>0.1049673202614379</v>
       </c>
-      <c r="U45" t="n">
+      <c r="W45" t="n">
         <v>0.06492248062015504</v>
       </c>
-      <c r="V45" t="n">
+      <c r="X45" t="n">
         <v>0.03547609876207524</v>
       </c>
-      <c r="W45" t="n">
+      <c r="Y45" t="n">
         <v>0.1071780932246049</v>
       </c>
-      <c r="X45" t="n">
+      <c r="Z45" t="n">
         <v>0.1527777777777778</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="AA45" t="n">
         <v>0.03340263340263341</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="AB45" t="n">
         <v>0.07044952804100428</v>
       </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
         <v>0.03598246373389995</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AD45" t="n">
         <v>0.03406936882435975</v>
       </c>
-      <c r="AC45" t="n">
+      <c r="AE45" t="n">
         <v>0.06986802211521313</v>
       </c>
-      <c r="AD45" t="n">
+      <c r="AF45" t="n">
         <v>0.04480502136752137</v>
       </c>
-      <c r="AE45" t="n">
+      <c r="AG45" t="n">
         <v>0.03772805931079312</v>
       </c>
-      <c r="AF45" t="n">
+      <c r="AH45" t="n">
         <v>0.05000924000924001</v>
       </c>
-      <c r="AG45" t="n">
+      <c r="AI45" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5214,104 +5664,114 @@
       <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>355.721</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>348.753</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
         <v>77.7</v>
       </c>
-      <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="n">
+      <c r="E46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" t="n">
         <v>22.3</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
         <v>64.86</v>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t xml:space="preserve">  He finds the ball, but not the other boy.  His friend is nowhere to be seen.</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>0.02312138728323699</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>0.03439153439153439</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>0.08950079392742342</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
         <v>0.03448275862068965</v>
       </c>
-      <c r="L46" t="n">
+      <c r="N46" t="n">
         <v>0.026378896882494</v>
       </c>
-      <c r="M46" t="n">
+      <c r="O46" t="n">
         <v>0.08090209020902089</v>
       </c>
-      <c r="N46" t="n">
+      <c r="P46" t="n">
         <v>0.03411729232624755</v>
       </c>
-      <c r="O46" t="n">
+      <c r="Q46" t="n">
         <v>0.02777777777777778</v>
       </c>
-      <c r="P46" t="n">
+      <c r="R46" t="n">
         <v>0.06402918069584736</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="S46" t="n">
         <v>0.05950774371827004</v>
       </c>
-      <c r="R46" t="n">
+      <c r="T46" t="n">
         <v>1.5</v>
       </c>
-      <c r="S46" t="n">
+      <c r="U46" t="n">
         <v>0.1374647887323944</v>
       </c>
-      <c r="T46" t="n">
+      <c r="V46" t="n">
         <v>0.1674509803921569</v>
       </c>
-      <c r="U46" t="n">
+      <c r="W46" t="n">
         <v>0.0782170542635659</v>
       </c>
-      <c r="V46" t="n">
+      <c r="X46" t="n">
         <v>0.03191489361702127</v>
       </c>
-      <c r="W46" t="n">
+      <c r="Y46" t="n">
         <v>0.07272727272727272</v>
       </c>
-      <c r="X46" t="n">
+      <c r="Z46" t="n">
         <v>0.234508547008547</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="AA46" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
         <v>0.05434782608695652</v>
       </c>
-      <c r="AD46" t="n">
+      <c r="AF46" t="n">
         <v>0.06097560975609756</v>
       </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
         <v>0.007407407407407408</v>
       </c>
-      <c r="AG46" t="n">
+      <c r="AI46" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -5319,104 +5779,114 @@
       <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>365.379</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>357.824</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
         <v>51.9</v>
       </c>
-      <c r="C47" t="n">
+      <c r="E47" t="n">
         <v>35.09999999999999</v>
       </c>
-      <c r="D47" t="n">
+      <c r="F47" t="n">
         <v>13</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
         <v>-52.66999999999999</v>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t xml:space="preserve"> Disappointed, the boy abandons the ball and slowly leaves the dream.</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>0.01415094339622642</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>0.02040816326530612</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>0.04830738818878182</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
         <v>0.01907114624505929</v>
       </c>
-      <c r="L47" t="n">
+      <c r="N47" t="n">
         <v>0.02830188679245283</v>
       </c>
-      <c r="M47" t="n">
+      <c r="O47" t="n">
         <v>0.110251572327044</v>
       </c>
-      <c r="N47" t="n">
+      <c r="P47" t="n">
         <v>0.06375813241484883</v>
       </c>
-      <c r="O47" t="n">
+      <c r="Q47" t="n">
         <v>0.09159482758620691</v>
       </c>
-      <c r="P47" t="n">
+      <c r="R47" t="n">
         <v>0.04848484848484848</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="S47" t="n">
         <v>0.08428680396643783</v>
       </c>
-      <c r="R47" t="n">
+      <c r="T47" t="n">
         <v>1.333333333333333</v>
       </c>
-      <c r="S47" t="n">
+      <c r="U47" t="n">
         <v>0.2777777777777778</v>
       </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
       <c r="V47" t="n">
         <v>0</v>
       </c>
       <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
       <c r="Z47" t="n">
         <v>0</v>
       </c>
       <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
         <v>0.3888888888888889</v>
       </c>
-      <c r="AB47" t="n">
+      <c r="AD47" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="AC47" t="n">
+      <c r="AE47" t="n">
         <v>0.1538461538461539</v>
       </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
         <v>0.06666666666666667</v>
       </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
         <v>0.1666666666666667</v>
       </c>
     </row>
@@ -5424,104 +5894,114 @@
       <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>381.118</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>366.2</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
         <v>100</v>
       </c>
-      <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="n">
-        <v>0</v>
-      </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t xml:space="preserve">  He sleeps the rest of the night.  In the morning, the boy's father wakes up and calls for him from the bottom of the stairs.</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>0.03885630498533725</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>0.04067892275439446</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>0.09952842298443879</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
         <v>0.03483606557377049</v>
       </c>
-      <c r="L48" t="n">
+      <c r="N48" t="n">
         <v>0.02272727272727273</v>
       </c>
-      <c r="M48" t="n">
+      <c r="O48" t="n">
         <v>0.06939024390243903</v>
       </c>
-      <c r="N48" t="n">
+      <c r="P48" t="n">
         <v>0.03467469283417168</v>
       </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
         <v>0.07323232323232323</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="S48" t="n">
         <v>0.06307667034762213</v>
       </c>
-      <c r="R48" t="n">
+      <c r="T48" t="n">
         <v>0.8</v>
       </c>
-      <c r="S48" t="n">
+      <c r="U48" t="n">
         <v>0.06818181818181819</v>
       </c>
-      <c r="T48" t="n">
+      <c r="V48" t="n">
         <v>0.05128205128205129</v>
       </c>
-      <c r="U48" t="n">
+      <c r="W48" t="n">
         <v>0.0837121212121212</v>
       </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
         <v>0.05314009661835748</v>
       </c>
-      <c r="X48" t="n">
+      <c r="Z48" t="n">
         <v>0.1918456918456919</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="AA48" t="n">
         <v>0.09135802469135802</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="AB48" t="n">
         <v>0.07631578947368421</v>
       </c>
-      <c r="AA48" t="n">
+      <c r="AC48" t="n">
         <v>0.1546218487394958</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AD48" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AE48" t="n">
         <v>0.1283735184663977</v>
       </c>
-      <c r="AD48" t="n">
+      <c r="AF48" t="n">
         <v>0.121587186021114</v>
       </c>
-      <c r="AE48" t="n">
+      <c r="AG48" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="AF48" t="n">
+      <c r="AH48" t="n">
         <v>0.0202020202020202</v>
       </c>
-      <c r="AG48" t="n">
+      <c r="AI48" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -5529,67 +6009,71 @@
       <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>385.763</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>381.718</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
         <v>100</v>
       </c>
-      <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boy wakes up, gets out of bed, and walks downstairs.</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>0.01932367149758454</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>0.0712387028176502</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
       <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
         <v>0.1560038986354776</v>
       </c>
-      <c r="N49" t="n">
+      <c r="P49" t="n">
         <v>0.01492537313432836</v>
       </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
         <v>0.04242424242424242</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="S49" t="n">
         <v>0.05096073517126148</v>
       </c>
-      <c r="R49" t="n">
+      <c r="T49" t="n">
         <v>1</v>
       </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
       <c r="U49" t="n">
         <v>0</v>
       </c>
@@ -5600,33 +6084,39 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
         <v>0.4</v>
       </c>
-      <c r="Y49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>0</v>
-      </c>
       <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="AB49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" t="n">
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
-      </c>
       <c r="AF49" t="n">
         <v>0</v>
       </c>
       <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -5634,104 +6124,114 @@
       <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>390.083</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>386.637</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
         <v>100</v>
       </c>
-      <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="n">
-        <v>0</v>
-      </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="inlineStr">
         <is>
           <t xml:space="preserve"> Father and son exchange a few words and the boy heads out.</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>0.03184973458554512</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>0.0379454926624738</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>0.04710182318541453</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
         <v>0.01507537688442211</v>
       </c>
-      <c r="L50" t="n">
+      <c r="N50" t="n">
         <v>0.04079511497986228</v>
       </c>
-      <c r="M50" t="n">
+      <c r="O50" t="n">
         <v>0.0894716066510589</v>
       </c>
-      <c r="N50" t="n">
+      <c r="P50" t="n">
         <v>0.04203405834783828</v>
       </c>
-      <c r="O50" t="n">
+      <c r="Q50" t="n">
         <v>0.0451587646194227</v>
       </c>
-      <c r="P50" t="n">
+      <c r="R50" t="n">
         <v>0.05984105324167436</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="S50" t="n">
         <v>0.06018946450933953</v>
       </c>
-      <c r="R50" t="n">
+      <c r="T50" t="n">
         <v>6</v>
       </c>
-      <c r="S50" t="n">
+      <c r="U50" t="n">
         <v>0.04838709677419355</v>
       </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
         <v>0.021875</v>
       </c>
-      <c r="V50" t="n">
+      <c r="X50" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="W50" t="n">
+      <c r="Y50" t="n">
         <v>0.1711794772256729</v>
       </c>
-      <c r="X50" t="n">
+      <c r="Z50" t="n">
         <v>0.3429749069283953</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="AA50" t="n">
         <v>0.01282051282051282</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="AB50" t="n">
         <v>0.09267967696332526</v>
       </c>
-      <c r="AA50" t="n">
+      <c r="AC50" t="n">
         <v>0.1475305670549726</v>
       </c>
-      <c r="AB50" t="n">
+      <c r="AD50" t="n">
         <v>0.07101393188854489</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AE50" t="n">
         <v>0.1158492822966507</v>
       </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
       <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
         <v>0.06202651515151515</v>
       </c>
-      <c r="AG50" t="n">
+      <c r="AI50" t="n">
         <v>2</v>
       </c>
     </row>
@@ -5739,104 +6239,114 @@
       <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>395.332</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>390.584</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
         <v>100</v>
       </c>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boy walks to the playground where his ball is still sitting at the far end of the yard.</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
       <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
         <v>0.03070175438596491</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
         <v>0.01712328767123288</v>
       </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
         <v>0.1038570199340313</v>
       </c>
-      <c r="N51" t="n">
+      <c r="P51" t="n">
         <v>0.06121334792280267</v>
       </c>
-      <c r="O51" t="n">
+      <c r="Q51" t="n">
         <v>0.06499298208367243</v>
       </c>
-      <c r="P51" t="n">
+      <c r="R51" t="n">
         <v>0.08076818687839839</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="S51" t="n">
         <v>0.07418505632345712</v>
       </c>
-      <c r="R51" t="n">
+      <c r="T51" t="n">
         <v>1</v>
       </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
         <v>0.1145251396648045</v>
       </c>
-      <c r="U51" t="n">
+      <c r="W51" t="n">
         <v>0.07584269662921349</v>
       </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
       <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
         <v>0.05612244897959184</v>
       </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
         <v>0.1493506493506493</v>
       </c>
-      <c r="AA51" t="n">
+      <c r="AC51" t="n">
         <v>0.0735930735930736</v>
       </c>
-      <c r="AB51" t="n">
+      <c r="AD51" t="n">
         <v>0.07881773399014778</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AE51" t="n">
         <v>0.1191408821593153</v>
       </c>
-      <c r="AD51" t="n">
+      <c r="AF51" t="n">
         <v>0.1196682898253579</v>
       </c>
-      <c r="AE51" t="n">
+      <c r="AG51" t="n">
         <v>0.0379746835443038</v>
       </c>
-      <c r="AF51" t="n">
+      <c r="AH51" t="n">
         <v>0.09265076594919527</v>
       </c>
-      <c r="AG51" t="n">
+      <c r="AI51" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -5844,73 +6354,77 @@
       <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>404.547</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>395.833</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>100</v>
       </c>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boy enters the playground, closing the gate after himself.</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
       <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
         <v>0.06140350877192983</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
         <v>0.04117647058823529</v>
       </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
         <v>0.1341176470588235</v>
       </c>
-      <c r="N52" t="n">
+      <c r="P52" t="n">
         <v>0.05747577899973814</v>
       </c>
-      <c r="O52" t="n">
+      <c r="Q52" t="n">
         <v>0.03731343283582089</v>
       </c>
-      <c r="P52" t="n">
+      <c r="R52" t="n">
         <v>0.06363636363636363</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="S52" t="n">
         <v>0.05263157894736842</v>
       </c>
-      <c r="R52" t="n">
+      <c r="T52" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
         <v>0.2272727272727273</v>
       </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
       <c r="W52" t="n">
         <v>0</v>
       </c>
@@ -5921,27 +6435,33 @@
         <v>0</v>
       </c>
       <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="n">
         <v>0.2777777777777778</v>
       </c>
-      <c r="AC52" t="n">
+      <c r="AE52" t="n">
         <v>0.2083333333333333</v>
       </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
-      </c>
       <c r="AF52" t="n">
         <v>0</v>
       </c>
       <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
         <v>0.25</v>
       </c>
     </row>
@@ -5949,46 +6469,50 @@
       <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>418.984</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>406.591</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
         <v>100</v>
       </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t xml:space="preserve">  He forlornly walks to the single ball.  He slowly and unenthusiastically kicks the ball halfway down the yard.</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>0.1292517006802721</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>0.1167883211678832</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
         <v>0.1027397260273972</v>
       </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
@@ -5999,44 +6523,44 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="R53" t="n">
+      <c r="T53" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
       <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
         <v>0.1454545454545454</v>
       </c>
-      <c r="V53" t="n">
+      <c r="X53" t="n">
         <v>0.1636363636363636</v>
       </c>
-      <c r="W53" t="n">
+      <c r="Y53" t="n">
         <v>0.196078431372549</v>
       </c>
-      <c r="X53" t="n">
+      <c r="Z53" t="n">
         <v>0.1730769230769231</v>
       </c>
-      <c r="Y53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" t="n">
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
         <v>0.2391304347826087</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AC53" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
       <c r="AD53" t="n">
         <v>0</v>
       </c>
@@ -6044,9 +6568,15 @@
         <v>0</v>
       </c>
       <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
         <v>0.08163265306122448</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AI53" t="n">
         <v>0.1111111111111111</v>
       </c>
     </row>
@@ -6054,52 +6584,56 @@
       <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>427.766</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>421.891</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
         <v>75.5</v>
       </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
         <v>24.5</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
         <v>63.69</v>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t xml:space="preserve"> As he kicks the ball again, his mysterious friend from the dream appears and sneaks towards the playground.</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>0.04198931181153889</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>0.07978423692709406</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>0.0969614181966217</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
         <v>0.08661519408645846</v>
       </c>
-      <c r="L54" t="n">
+      <c r="N54" t="n">
         <v>0.07177758118813991</v>
       </c>
-      <c r="M54" t="n">
+      <c r="O54" t="n">
         <v>0.02439024390243902</v>
       </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
       <c r="P54" t="n">
         <v>0</v>
       </c>
@@ -6107,51 +6641,57 @@
         <v>0</v>
       </c>
       <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
         <v>0.6</v>
       </c>
-      <c r="S54" t="n">
+      <c r="U54" t="n">
         <v>0.1447457627118644</v>
       </c>
-      <c r="T54" t="n">
+      <c r="V54" t="n">
         <v>0.2092691622103387</v>
       </c>
-      <c r="U54" t="n">
+      <c r="W54" t="n">
         <v>0.07334525939177103</v>
       </c>
-      <c r="V54" t="n">
+      <c r="X54" t="n">
         <v>0.03191489361702127</v>
       </c>
-      <c r="W54" t="n">
+      <c r="Y54" t="n">
         <v>0.1181818181818182</v>
       </c>
-      <c r="X54" t="n">
+      <c r="Z54" t="n">
         <v>0.2401315789473684</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="AA54" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
       <c r="AB54" t="n">
         <v>0</v>
       </c>
       <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
         <v>0.03968253968253968</v>
       </c>
-      <c r="AD54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" t="n">
-        <v>0</v>
-      </c>
       <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
         <v>0.01428571428571429</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AI54" t="n">
         <v>0.3333333333333333</v>
       </c>
     </row>
@@ -6159,104 +6699,114 @@
       <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>431.595</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>427.906</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
         <v>77.5</v>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
         <v>22.5</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
         <v>49.39</v>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t xml:space="preserve">  He checks that his friend is there.  He quietly opens the gate.</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>0.02312138728323699</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>0.1113146113146113</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>0.04856512141280353</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
         <v>0.07151979565772669</v>
       </c>
-      <c r="L55" t="n">
+      <c r="N55" t="n">
         <v>0.03971223021582734</v>
       </c>
-      <c r="M55" t="n">
+      <c r="O55" t="n">
         <v>0.04738562091503268</v>
       </c>
-      <c r="N55" t="n">
+      <c r="P55" t="n">
         <v>0.07555555555555556</v>
       </c>
-      <c r="O55" t="n">
+      <c r="Q55" t="n">
         <v>0.07627627627627627</v>
       </c>
-      <c r="P55" t="n">
+      <c r="R55" t="n">
         <v>0.07344632768361582</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="S55" t="n">
         <v>0.01333333333333333</v>
       </c>
-      <c r="R55" t="n">
+      <c r="T55" t="n">
         <v>1.5</v>
       </c>
-      <c r="S55" t="n">
+      <c r="U55" t="n">
         <v>0.4830769230769231</v>
       </c>
-      <c r="T55" t="n">
+      <c r="V55" t="n">
         <v>0.1274509803921569</v>
       </c>
-      <c r="U55" t="n">
+      <c r="W55" t="n">
         <v>0.09738372093023256</v>
       </c>
-      <c r="V55" t="n">
+      <c r="X55" t="n">
         <v>0.03191489361702127</v>
       </c>
-      <c r="W55" t="n">
+      <c r="Y55" t="n">
         <v>0.2155844155844156</v>
       </c>
-      <c r="X55" t="n">
+      <c r="Z55" t="n">
         <v>0.1875</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="AA55" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
       <c r="AB55" t="n">
         <v>0</v>
       </c>
       <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="n">
         <v>0.09523809523809523</v>
       </c>
-      <c r="AD55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" t="n">
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
         <v>0.02380952380952381</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AH55" t="n">
         <v>0.08</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AI55" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -6264,67 +6814,71 @@
       <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>438.51</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>433.702</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
         <v>100</v>
       </c>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="inlineStr">
         <is>
           <t xml:space="preserve">  He sneaks up on the boy who still doesn't see him.  He taps the boy on the shoulder.</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>0.01960784313725491</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>0.1085380116959064</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
         <v>0.01388888888888889</v>
       </c>
-      <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
         <v>0.2366666666666667</v>
       </c>
-      <c r="N56" t="n">
+      <c r="P56" t="n">
         <v>0.02985074626865672</v>
       </c>
-      <c r="O56" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" t="n">
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
         <v>0.08484848484848484</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="S56" t="n">
         <v>0.07017543859649122</v>
       </c>
-      <c r="R56" t="n">
+      <c r="T56" t="n">
         <v>1.5</v>
       </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
       <c r="U56" t="n">
         <v>0</v>
       </c>
@@ -6362,6 +6916,12 @@
         <v>0</v>
       </c>
       <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6369,104 +6929,114 @@
       <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>441.755</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>438.61</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
         <v>76.3</v>
       </c>
-      <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="n">
+      <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
         <v>23.7</v>
       </c>
-      <c r="E57" t="n">
+      <c r="G57" t="n">
         <v>47.67</v>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t xml:space="preserve">  The boy whirls around.  The two friends talk back and forth.</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>0.04265402843601895</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>0.0648827847501776</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>0.1231062151502788</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
         <v>0.06545688866716554</v>
       </c>
-      <c r="L57" t="n">
+      <c r="N57" t="n">
         <v>0.04594708025715866</v>
       </c>
-      <c r="M57" t="n">
+      <c r="O57" t="n">
         <v>0.09608247422680412</v>
       </c>
-      <c r="N57" t="n">
+      <c r="P57" t="n">
         <v>0.01492537313432836</v>
       </c>
-      <c r="O57" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" t="n">
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
         <v>0.04242424242424242</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="S57" t="n">
         <v>0.03508771929824561</v>
       </c>
-      <c r="R57" t="n">
+      <c r="T57" t="n">
         <v>1.5</v>
       </c>
-      <c r="S57" t="n">
+      <c r="U57" t="n">
         <v>0.1398026315789474</v>
       </c>
-      <c r="T57" t="n">
+      <c r="V57" t="n">
         <v>0.2197357203751066</v>
       </c>
-      <c r="U57" t="n">
+      <c r="W57" t="n">
         <v>0.2089825119236884</v>
       </c>
-      <c r="V57" t="n">
+      <c r="X57" t="n">
         <v>0.1081081081081081</v>
       </c>
-      <c r="W57" t="n">
+      <c r="Y57" t="n">
         <v>0.1463719022998752</v>
       </c>
-      <c r="X57" t="n">
+      <c r="Z57" t="n">
         <v>0.284180790960452</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="AA57" t="n">
         <v>0.03571428571428571</v>
       </c>
-      <c r="Z57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA57" t="n">
-        <v>0</v>
-      </c>
       <c r="AB57" t="n">
         <v>0</v>
       </c>
       <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="n">
         <v>0.08536585365853659</v>
       </c>
-      <c r="AD57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" t="n">
-        <v>0</v>
-      </c>
       <c r="AF57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" t="n">
         <v>0.02564102564102564</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AI57" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -6474,104 +7044,114 @@
       <c r="A58" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>444.98</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>441.875</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
         <v>21.1</v>
       </c>
-      <c r="E58" t="n">
+      <c r="G58" t="n">
         <v>49.39</v>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t xml:space="preserve"> The boy races to get his ball as his friend gets in position.</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>shapessocial_transcription_x.txt</t>
         </is>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>0.01387283236994219</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>0.05550498560243686</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>0.1127878672936902</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
         <v>0.03996676360614874</v>
       </c>
-      <c r="L58" t="n">
+      <c r="N58" t="n">
         <v>0.02599682965492013</v>
       </c>
-      <c r="M58" t="n">
+      <c r="O58" t="n">
         <v>0.08666110562818553</v>
       </c>
-      <c r="N58" t="n">
+      <c r="P58" t="n">
         <v>0.04138765631302944</v>
       </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
         <v>0.03924764890282131</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="S58" t="n">
         <v>0.03708806900973364</v>
       </c>
-      <c r="R58" t="n">
+      <c r="T58" t="n">
         <v>5</v>
       </c>
-      <c r="S58" t="n">
+      <c r="U58" t="n">
         <v>0.1824489795918367</v>
       </c>
-      <c r="T58" t="n">
+      <c r="V58" t="n">
         <v>0.1756437514764942</v>
       </c>
-      <c r="U58" t="n">
+      <c r="W58" t="n">
         <v>0.1887298747763864</v>
       </c>
-      <c r="V58" t="n">
+      <c r="X58" t="n">
         <v>0.03191489361702127</v>
       </c>
-      <c r="W58" t="n">
+      <c r="Y58" t="n">
         <v>0.07272727272727272</v>
       </c>
-      <c r="X58" t="n">
+      <c r="Z58" t="n">
         <v>0.2252358490566038</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="AA58" t="n">
         <v>0.02702702702702703</v>
       </c>
-      <c r="Z58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA58" t="n">
-        <v>0</v>
-      </c>
       <c r="AB58" t="n">
         <v>0</v>
       </c>
       <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="n">
         <v>0.08904109589041095</v>
       </c>
-      <c r="AD58" t="n">
+      <c r="AF58" t="n">
         <v>0.1319444444444444</v>
       </c>
-      <c r="AE58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" t="n">
-        <v>0</v>
-      </c>
       <c r="AG58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="n">
         <v>0.5</v>
       </c>
     </row>
